--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0205.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0205.xlsx
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Ừ, hệ thống của nó lại trục trặc từ bản cập nhật trước. Ta nghĩ là linh kiện mới không tương thích, nên phải điều chỉnh lại thôi.</t>
+          <t>Ừ, hệ thống của nó lại trục trặc từ bản cập nhật trước. Tao nghĩ là linh kiện mới không tương thích, nên phải điều chỉnh lại thôi.</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Dậy đi! Đến lượt ta sạc pin rồi—</t>
+          <t>Dậy đi! Đến lượt tao sạc pin rồi—</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Hôm qua Adrian nâng cấp phần cứng cho ta, giờ ta chỉ có thể dùng trạm sạc này thôi.</t>
+          <t>Hôm qua Adrian nâng cấp phần cứng cho tao, giờ tao chỉ có thể dùng trạm sạc này thôi.</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Được rồi, chúng ta có thể chia sẻ. Nhưng để ta chỗ nào đó với.</t>
+          <t>Được rồi, chúng ta có thể chia sẻ. Nhưng để tao chỗ nào đó với.</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Gì cơ? Đừng nhìn ta—ta chỉ còn mỗi chai si-rô phong thôi.</t>
+          <t>Gì cơ? Đừng nhìn tao—tao chỉ còn mỗi chai si-rô phong thôi.</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Khi ta quay lại, ta sẽ mang về cho ngươi vài thứ từ chỗ đó. Coi như trao đổi, thế nào?</t>
+          <t>Khi tao quay lại, tao sẽ mang về cho mày vài thứ từ chỗ đó. Coi như trao đổi, thế nào?</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Tỉnh queo thì tờ giấy đã biến mất tiêu, như sương khói vậy! Ta còn tưởng mình hoa mắt nữa chứ.</t>
+          <t>Tỉnh queo thì tờ giấy đã biến mất tiêu, như sương khói vậy! Tao còn tưởng mình hoa mắt nữa chứ.</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Không tin được luôn—cái cây nó nói chuyện với ta đấy! Nó còn cho ta một mẹo nữa cơ—</t>
+          <t>Không tin được luôn—cái cây nó nói chuyện với tao đấy! Nó còn cho tao một mẹo nữa cơ—</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>"Cosmos bảo ta rằng cứu thế giới khó như đánh bại Con Quỷ Đại Ác vậy. Làm một chiến binh đâu có dễ dàng gì."</t>
+          <t>"Cosmos bảo tao rằng cứu thế giới khó như đánh bại Con Quỷ Đại Ác vậy. Làm một chiến binh đâu có dễ dàng gì."</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Ta bảo đưa ta tên của chúng! Tất cả bọn chúng, không thiếu một đứa nào!</t>
+          <t>Tao bảo đưa tao tên của chúng! Tất cả bọn chúng, không thiếu một đứa nào!</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Ta phải nói bao nhiêu lần nữa mới được? KHÔNG CÓ NGHĨA LÀ KHÔNG!</t>
+          <t>Tao phải nói bao nhiêu lần nữa mới được? KHÔNG CÓ NGHĨA LÀ KHÔNG!</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Aaaaa! Ai đó xóa giùm ta mấy chữ này khỏi trí nhớ đi!</t>
+          <t>Aaaaa! Ai đó xóa giùm tao mấy chữ này khỏi trí nhớ đi!</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Bạn thấy Monica cau cậu, rõ ràng đang lo lắng điều gì đó.</t>
+          <t>Bạn thấy Monica cau mày, rõ ràng đang lo lắng điều gì đó.</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Ha, đoán chắc mặt ta lộ hết rồi nhỉ? Thực ra cũng hơi phức tạp đấy.</t>
+          <t>Ha, đoán chắc mặt tao lộ hết rồi nhỉ? Thực ra cũng hơi phức tạp đấy.</t>
         </is>
       </c>
     </row>
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Tin tốt cho mọi người nè! Ta vừa được KU-Money ủy quyền và làm cái này—</t>
+          <t>Tin tốt cho mọi người nè! Tao vừa được KU-Money ủy quyền và làm cái này—</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>ĐỢI ĐÃ! Cậu tạo ra thân xác này chỉ để bắt ta làm thêm việc thôi à?</t>
+          <t>ĐỢI ĐÃ! Cậu tạo ra thân xác này chỉ để bắt tao làm thêm việc thôi à?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chỉ mình cậu mới có câu trả lời, phải không? Anh ấy he he...</t>
+          <t>Chỉ mình cậu mới có câu trả lời, phải không? He he he...</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Không có gì cả. Ta chỉ đi dạo thôi.</t>
+          <t>Không có gì cả. Tao chỉ đi dạo thôi.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Xin chào, cậu đến đây có việc gì không? Có chuyện gì xảy ra với các bồn sinh học à?</t>
+          <t>Xin chào, bạn đến đây có việc gì không? Có chuyện gì xảy ra với các bồn sinh học à?</t>
         </is>
       </c>
     </row>
@@ -15979,7 +15979,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Bạn không biết à? Ồ, chắc hẳn cậu là Rover mới rồi! Tớ là Chengshi, người trồng cây ở Bờ Đen đây.</t>
+          <t>Bạn không biết à? Ồ, chắc hẳn cậu là Vận Mệnh Giả mới rồi! Tớ là Chengshi, người trồng cây ở Bờ Đen đây.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Việc mở lối thông giữa các không gian khác nhau sử dụng đặc tính không gian của Quả Cầu Sonoro.</t>
+          <t>Việc mở lối thông giữa các không gian khác nhau sử dụng đặc tính không gian của Sonoro Sphere.</t>
         </is>
       </c>
     </row>
